--- a/ESTA_バリデーション確認テストシート.xlsx
+++ b/ESTA_バリデーション確認テストシート.xlsx
@@ -7,20 +7,24 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step1 必須項目" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step2 渡航情報" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step3 個人情報" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step4 確認画面" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step5 お支払い" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step6 申請完了" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step1 確認テスト" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step1 必須項目" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step3 確認テスト" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step2 渡航情報" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step3 個人情報" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step4 確認画面" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step5 お支払い" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step6 申請完了" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Step1 必須項目'!$A$1:$H$117</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Step2 渡航情報'!$A$1:$H$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Step3 個人情報'!$A$1:$H$72</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Step4 確認画面'!$A$1:$H$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Step5 お支払い'!$A$1:$H$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Step6 申請完了'!$A$1:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Step1 確認テスト'!$A$1:$H$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Step1 必須項目'!$A$1:$H$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Step3 確認テスト'!$A$1:$H$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Step2 渡航情報'!$A$1:$H$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Step3 個人情報'!$A$1:$H$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Step4 確認画面'!$A$1:$H$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Step5 お支払い'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Step6 申請完了'!$A$1:$H$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -451,6 +455,3821 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H118"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>セクション</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>フィールド</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>確認項目</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>テスト操作</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>結果(○/×)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>姓</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>プレースホルダー</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>姓フィールドを空のまま確認</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>「(例) YAMADA」が表示</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>姓</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>必須チェック</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>空欄で次画面ボタン</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>エラー表示/進めない</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>姓</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>文字数上限(45字)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>46文字入力</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>45文字で止まる</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>姓</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>英字のみ</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>「YAMADA123」入力</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>数字除去「YAMADA」</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>姓</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>日本語入力不可</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>「やまだ」入力</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>除去される</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>姓</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>記号入力不可</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>「YAMADA@#$」入力</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>記号除去「YAMADA」</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>姓</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>小文字→大文字</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>「yamada」入力</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>「YAMADA」に変換</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>姓</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>スペース正規化</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>「YAMADA   TANAKA」入力</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>「YAMADA TANAKA」に</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>姓</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>前後スペース削除</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>「 YAMADA 」→blur</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>「YAMADA」に</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>姓</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>苗字アラート</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>一般的でない姓を入力</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>確認アラート表示</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>姓</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>エラーメッセージ</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>不正文字入力</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>「半角英字で入力してください」表示</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>姓</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>エラー時ボタン非アクティブ</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>エラー表示状態</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>ボタン非アクティブ</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>名</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>プレースホルダー</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>フィールド確認</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>「(例) TARO」表示</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>名</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>項目下注記</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>フィールド下確認</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>パスポート記載通りの注記</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>名</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>必須/45字/英字/大文字/trim</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>各テスト</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>全て姓と同様に動作</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>別名有無</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>デフォルト値</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>ページロード</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>「別名はありません」選択</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>別名有無</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Yes→入力欄表示</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>「別名があります」クリック</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>姓名(別名)表示</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>別名有無</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>No→非表示</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>「別名はありません」に戻す</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>入力欄非表示</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>姓(別名)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>全バリデーション</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>姓と同じテスト操作</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>同一動作</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>名(別名)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>全バリデーション</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>名と同じテスト操作</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>同一動作</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>デフォルト(未選択)</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>ページロード</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>どちらも未選択</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>男性選択</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>「男性」クリック</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>選択状態</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>女性選択</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>「女性」クリック</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>選択状態</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>DEU時Unspecified</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>国籍DEU選択</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>「Unspecified」追加</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>生年月日</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>デフォルト値</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>ページロード</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Year年Month月Day日</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>生年月日</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>正常入力</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>1990/1/15選択</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>エラーなし</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>生年月日</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>未来日</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>来年の日付選択</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>エラー表示+月日リセット</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>国籍</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>デフォルトJPN</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>ページロード</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>JAPAN(JPN)選択</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>国籍</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>検索機能</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>「korea」入力</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>SOUTH KOREA絞り込み</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>国籍</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>未選択時ボタン</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>未選択状態</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>ボタン非アクティブ</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>個人識別番号</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>BEL選択→表示</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>国籍BEL選択</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>フィールド表示</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>個人識別番号</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>JPN→非表示</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>国籍JPN</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>フィールド非表示</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>個人識別番号</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>全21カ国</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>各国を順に選択</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>全て表示</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>個人識別番号</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>任意(空欄OK)</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>空欄で次画面</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>エラーなし</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>個人識別番号</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>英数字のみ</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>記号入力</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>除去</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>個人識別番号</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>大文字/半角変換</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>小文字/全角入力</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>変換される</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>個人識別番号</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>スペース除去</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>スペース入力</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>除去</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>個人識別番号(TWN)</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>TWN→必須表示</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>国籍TWN</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>必須フィールド表示</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>個人識別番号(TWN)</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>正常入力</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>A123456789入力</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>エラーなし</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>個人識別番号(TWN)</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>不正形式</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>1234567890入力</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>エラー表示</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>個人識別番号(TWN)</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>10文字制限</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>11文字入力</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>10文字で止まる</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>連絡先情報</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>プレースホルダー</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>yamada_taro@example.co.jp表示</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>連絡先情報</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>必須/100字/形式チェック</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>不正メール入力→blur</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>エラー表示</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n"/>
+      <c r="H44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>連絡先情報</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>正常入力</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>test@example.com</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>エラーなし</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>連絡先情報</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>ハイフン変換</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>全角ハイフン入力</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>半角に変換</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>連絡先情報</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>スペース削除</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>前後スペース→blur</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>trimされる</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>連絡先情報</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>メール(確認)</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>一致OK</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>同じメール入力</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>エラーなし</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>連絡先情報</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>メール(確認)</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>一致NG</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>異なるメール入力</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>「一致しません」表示</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n"/>
+      <c r="H49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>連絡先情報</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>電話番号(国番号)</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>デフォルト</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>ページロード</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>JAPAN (+81)</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>連絡先情報</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>電話番号</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>数字のみ/20字</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>英字+21桁入力</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>英字除去+20桁制限</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>連絡先情報</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>電話番号</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>全角→半角</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>全角数字入力</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>半角に変換</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>連絡先情報</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>電話番号</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>ハイフン・スペース除去</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>090-1234-5678入力</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>09012345678に</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>連絡先情報</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>電話種別</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>4択</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>プルダウン開く</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>自宅/勤務先/携帯/その他</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>連絡先情報</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>電話種別</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>未選択時</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>「選択してください」状態</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>ボタン非アクティブ</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n"/>
+      <c r="H55" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>住所情報</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>郵便番号</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>数字のみ/10字</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>英字入力</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>除去</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n"/>
+      <c r="H56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>住所情報</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>郵便番号</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>自動入力</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>1000001入力</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>都道府県/市区町村自動入力</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="n"/>
+      <c r="H57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>住所情報</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>郵便番号</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>不正番号</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>9999999入力</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>アラート表示</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>住所情報</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>郵便番号</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>検索リンク</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>リンクをクリック</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>郵便局サイトに遷移</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n"/>
+      <c r="H59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>住所情報</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>国</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>デフォルトJPN</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>ページロード</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>JAPAN(JPN)選択</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n"/>
+      <c r="H60" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>住所情報</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>都道府県</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>60字/英字記号/数字不許可</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>TOKYO123入力</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>数字除去TOKYO</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="n"/>
+      <c r="H61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>住所情報</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>都道府県</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>大文字/半角/スペース/trim</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>tokyo入力→blur</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>TOKYO</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="n"/>
+      <c r="H62" s="4" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>住所情報</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>市区町村</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>70字/英数字記号</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>CHIYODA-KU 1入力</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>許可</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="n"/>
+      <c r="H63" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>住所情報</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>丁番地</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>60字/英数字記号</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>1-1-1入力</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>許可</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="n"/>
+      <c r="H64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>住所情報</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>建物名</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>60字/任意/英数字記号</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>空欄で次画面</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>エラーなし</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="n"/>
+      <c r="H65" s="4" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>住所情報</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>部屋番号</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>10字/任意/スペース除去</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>1 01入力</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>101に</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="n"/>
+      <c r="H66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>パスポートアップロード</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>ファイル選択</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>jpgファイルを選択</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>ファイル名が表示される</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="n"/>
+      <c r="H67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>パスポートアップロード</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>10MB超過</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>11MBファイルを選択</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>エラー「サイズが上限の10MBを超えています」</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="n"/>
+      <c r="H68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>パスポートアップロード</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>不正形式</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>txtファイルを選択</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>ファイル選択ダイアログで制限</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="n"/>
+      <c r="H69" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>顔写真アップロード</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>ファイル選択</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>jpgファイルを選択</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>ファイル名が表示</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="n"/>
+      <c r="H70" s="4" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>顔写真アップロード</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>10MB超過</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>大きいファイル選択</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>エラー表示</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="n"/>
+      <c r="H71" s="4" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>顔写真アップロード</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>gif不許可</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>gifファイルを選択</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>「jpeg,pngファイルのみ」エラー</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="n"/>
+      <c r="H72" s="4" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>顔写真アップロード</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>下部確認</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>パスポート顔写真使用不可の赤字注記</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="n"/>
+      <c r="H73" s="4" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>パスポート番号</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>プレースホルダー</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>(例) TH1234567</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="n"/>
+      <c r="H74" s="4" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>パスポート番号</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>JPN正常入力</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>TH1234567入力</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>エラーなし</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="n"/>
+      <c r="H75" s="4" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>パスポート番号</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>JPN不正入力</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>12345入力</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>エラー表示</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="n"/>
+      <c r="H76" s="4" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>パスポート番号</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>大文字変換</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>th1234567入力</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>TH1234567に変換</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="n"/>
+      <c r="H77" s="4" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>パスポート番号</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>KOR正常</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>M12345678入力(国籍KOR時)</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>エラーなし</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="n"/>
+      <c r="H78" s="4" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>パスポート番号</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>注記確認</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>下部確認</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>O(オー)と0(ゼロ)の混同注意</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="n"/>
+      <c r="H79" s="4" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>発行年月日</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>デフォルト</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>Day日/Month月/Year年</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="n"/>
+      <c r="H80" s="4" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>発行年月日</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>正常入力</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>2020/1/15選択</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>エラーなし</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="n"/>
+      <c r="H81" s="4" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>発行年月日</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>DOBより前</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>DOB以前の日付</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>エラー表示</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="n"/>
+      <c r="H82" s="4" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>発行年月日</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>未来日</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>明日以降の日付</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>エラー表示</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="n"/>
+      <c r="H83" s="4" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>有効期間満了日</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>正常入力</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>2030/1/15選択</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>エラーなし</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="n"/>
+      <c r="H84" s="4" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>有効期間満了日</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>過去日</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>昨日以前の日付</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>エラー表示</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="n"/>
+      <c r="H85" s="4" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>有効期間満了日</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>JPN T期間チェック</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>T始まり番号で発行日+10年1日</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>正常/不一致で訂正旅券注記</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="n"/>
+      <c r="H86" s="4" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>有効期間満了日</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>JPN M期間チェック</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>M始まり番号で発行日+5年1日</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>正常/不一致で訂正旅券注記</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="n"/>
+      <c r="H87" s="4" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>発行国</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>デフォルトJPN</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>ページロード</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>JAPAN(JPN)選択</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="n"/>
+      <c r="H88" s="4" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>発行国</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>下部確認</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>※通常は国籍と同じ</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="n"/>
+      <c r="H89" s="4" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>出生国</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>デフォルトJPN</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>ページロード</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>JAPAN(JPN)選択</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="n"/>
+      <c r="H90" s="4" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>出生都市</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>任意/空欄OK</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>空欄で次画面</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>エラーなし</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="n"/>
+      <c r="H91" s="4" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>出生都市</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>英数字入力</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>TOKYO入力</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="n"/>
+      <c r="H92" s="4" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>出生都市</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>不正文字</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>日本語入力</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>エラー表示</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="n"/>
+      <c r="H93" s="4" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>他国パスポート</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>デフォルトNo</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>ページロード</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>「いいえ」選択</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="n"/>
+      <c r="H94" s="4" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>他国パスポート</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Yes→詳細表示</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>「はい」クリック</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>発給国/種類/ID/期限の入力欄表示</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="n"/>
+      <c r="H95" s="4" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>他国パスポート</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>No→非表示</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>「いいえ」に戻す</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>入力欄非表示</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="n"/>
+      <c r="H96" s="4" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>発給国</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>プルダウン選択</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>国を選択</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>正常に選択</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="n"/>
+      <c r="H97" s="4" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>種類</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>プルダウン</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>選択肢確認</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>パスポート/国家身分証明書</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="n"/>
+      <c r="H98" s="4" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>ID番号</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>英数字入力</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>ABC123入力</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="n"/>
+      <c r="H99" s="4" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>ID番号</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>不正文字</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>日本語入力</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>エラー表示</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="n"/>
+      <c r="H100" s="4" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>有効期限</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>プルダウン</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>年選択</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN含む選択肢</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="n"/>
+      <c r="H101" s="4" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>他国籍(現在)</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>デフォルトNo</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>ページロード</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>「いいえ」選択</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="n"/>
+      <c r="H102" s="4" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>他国籍(現在)</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Yes→詳細表示</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>「はい」クリック</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>国選択+取得経緯表示</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="n"/>
+      <c r="H103" s="4" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>他国籍(現在)国</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>プルダウン選択</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>国を選択</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="n"/>
+      <c r="H104" s="4" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>取得経緯</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>プルダウン</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>選択肢確認</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>出生/両親/帰化/その他</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="n"/>
+      <c r="H105" s="4" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>他国籍(過去)</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>デフォルトNo</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>ページロード</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>「いいえ」選択</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="n"/>
+      <c r="H106" s="4" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>他国籍(過去)</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Yes→詳細表示</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>「はい」クリック</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>国選択+取得日+放棄日表示</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="n"/>
+      <c r="H107" s="4" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>他国籍(過去)国</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>プルダウン選択</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>国を選択</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="n"/>
+      <c r="H108" s="4" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>取得日</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>日付選択</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>2010/1/1選択</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="n"/>
+      <c r="H109" s="4" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>放棄日</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>日付選択</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>2020/1/1選択</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="n"/>
+      <c r="H110" s="4" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>放棄日</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>取得日より前</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>取得日以前の日付</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>エラー/警告</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="n"/>
+      <c r="H111" s="4" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>GE/NEXUS/SENTRI</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>デフォルトNo</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>ページロード</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>「いいえ」選択</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="n"/>
+      <c r="H112" s="4" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>GE/NEXUS/SENTRI</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>注記</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>下部確認</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>※ご存知でない方は「いいえ」</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="n"/>
+      <c r="H113" s="4" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>GE/NEXUS/SENTRI</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>Yes→PASS ID表示</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>「はい」クリック</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>PASS ID入力欄表示</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="n"/>
+      <c r="H114" s="4" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>PASS ID</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>正常入力(9桁)</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>123456789入力</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>エラーなし</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="n"/>
+      <c r="H115" s="4" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>PASS ID</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>8桁入力</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>12345678入力</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>エラー表示</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="n"/>
+      <c r="H116" s="4" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>パスポート情報</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>PASS ID</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>英字入力</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>ABC123456入力</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>エラー表示</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="n"/>
+      <c r="H117" s="4" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>申請者情報</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>姓(別名)</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>苗字アラート</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>別名「はい」→aliasSurnameに「SUZKI」入力→blur</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>⚠️アラート「もしかして SUZUKI ではありませんか？」が表示される</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="n"/>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>CSV仕様対応: attachSurnameAlert適用</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H118"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4224,7 +8043,2454 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>セクション</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>フィールド</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>確認項目</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>テスト操作</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>結果(○/×)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>就労経験</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>デフォルト値</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>ページ読み込み直後</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>はい/いいえ どちらも未選択</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>就労経験</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>はい→就労詳細表示</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>「はい」クリック</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>雇用者名/国/住所等の入力欄表示</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>就労経験</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>いいえ→雇用状況表示</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>「いいえ」クリック</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>雇用状況プルダウン表示</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>雇用者名</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>プレースホルダー</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>フィールド確認</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>「(例) ABC CORPORATION」表示</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>雇用者名</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>文字数(60字)</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>61文字入力</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>60文字で止まる</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>雇用者名</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>英数字+記号</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>「ABC CO. LTD」入力</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>許可される</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>雇用者名</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>大文字変換</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>「abc corporation」入力</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>「ABC CORPORATION」に変換</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>雇用者名</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>全角→半角</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>全角英字入力</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>半角に変換</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>雇用者名</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>スペース正規化</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>複数スペース入力</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>半角1つに</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>雇用者名</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>trim</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>前後スペース→blur</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>trimされる</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>雇用者名</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>エラー表示</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>不正文字入力</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>「半角英数字で入力してください」表示</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>雇用者 国</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>プルダウン選択</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>プルダウンを開く</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>世界各国リストが表示</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>雇用者 国</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>検索機能</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>「japan」と入力</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>JAPAN(JPN)が絞り込み表示</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>雇用者 都道府県</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>英字のみ</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>数字入力</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>除去される</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>雇用者 都道府県</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>大文字変換</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>「tokyo」入力</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>「TOKYO」に変換</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>雇用者 市区町村</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>英数字許可</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>「CHIYODA-KU 1」入力</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>許可される</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>雇用者 丁番地</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>英数字許可</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>「1-1-1 MARUNOUCHI」入力</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>許可される</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>雇用者 電話番号</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>数字のみ</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>英字入力</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>除去される</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>雇用者 電話番号</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>文字数(20字)</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>21桁入力</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>20桁で止まる</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>職名</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>プレースホルダー</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>フィールド確認</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>「(例) ENGINEER」表示</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>職名</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>英字のみ</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>数字入力</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>除去される</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>職名</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>大文字変換</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>「engineer」入力</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>「ENGINEER」に変換</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>雇用状況</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>デフォルト値</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>「いいえ」選択後</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>「選択してください」表示</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>雇用状況</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>選択肢</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>プルダウンを開く</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>学生/無職/退職/主婦・主夫/子供/その他の6つ</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>就労情報</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>雇用状況</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>選択操作</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>「学生」を選択</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>正常に選択される</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>SNS情報</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>登録有無</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>デフォルト値</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>ページ読み込み直後</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>はい/いいえ未選択</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>SNS情報</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>登録有無</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>はい→入力表示</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>「はい」クリック</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>SNSプラットフォーム+アカウント名の入力欄表示</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>SNS情報</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>登録有無</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>いいえ→非表示</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>「いいえ」クリック</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>入力欄非表示</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>SNS情報</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>プラットフォーム</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>選択肢</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>プルダウンを開く</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>FB/Insta/X/LinkedIn/YT/TikTok/Weibo/その他</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>SNS情報</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>アカウント名</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>プレースホルダー</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>フィールド確認</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>「(例) @yamada_taro」表示</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>SNS情報</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>アカウント名</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>入力</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>「@test_user」入力</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>正常に入力される</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>SNS情報</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>追加ボタン</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>複数エントリ追加</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>「＋SNSアカウントを追加」クリック</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>新しいSNS入力欄が追加される</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>SNS情報</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>追加ボタン</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>2回追加</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>追加ボタンを2回クリック</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>3つのSNSエントリが表示</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>SNS情報</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>削除ボタン</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>エントリ削除</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>追加エントリの×ボタンクリック</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>該当エントリが削除される</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>緊急連絡先</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>登録有無</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>デフォルト値</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>ページ読み込み直後</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>「いいえ」選択</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>緊急連絡先</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>登録有無</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>はい→入力表示</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>「はい」クリック</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>姓/名/メール/電話の入力欄表示</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>緊急連絡先</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>姓</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>英字のみ</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>数字入力</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>除去される</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>緊急連絡先</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>姓</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>大文字変換</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>「yamada」入力</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>「YAMADA」に変換</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>緊急連絡先</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>姓</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>文字数(40字)</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>41文字入力</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>40文字で止まる</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>緊急連絡先</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>姓</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>エラー表示</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>不正文字→blur</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>エラーメッセージ表示</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>緊急連絡先</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>名</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>英字のみ</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>数字入力</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>除去される</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>緊急連絡先</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>名</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>大文字変換</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>「hanako」入力</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>「HANAKO」に変換</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>緊急連絡先</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>メール</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>正常入力</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>「test@example.com」入力</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>エラーなし</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n"/>
+      <c r="H44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>緊急連絡先</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>電話番号</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>数字のみ</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>「090-abcd」入力</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>英字・ハイフン除去「090」</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>緊急連絡先</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>電話番号</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>文字数(20字)</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>21桁入力</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>20桁で止まる</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>両親情報</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>登録有無</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>デフォルト値</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>ページ読み込み直後</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>「いいえ」選択</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>両親情報</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>登録有無</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>はい→入力表示</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>「はい」クリック</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>父/母の姓名入力欄表示</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>両親情報</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>父Unknown</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>チェック→非表示</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>「不明/Unknown」にチェック</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>父の姓名入力欄が非表示</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n"/>
+      <c r="H49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>両親情報</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>父Unknown</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>チェック→値クリア</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>チェック入れた後、解除して確認</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>入力値がクリアされている</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>両親情報</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>父 姓</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>英字のみ</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>数字入力</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>除去される</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>両親情報</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>父 姓</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>大文字変換</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>「yamada」入力</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>「YAMADA」に変換</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>両親情報</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>父 姓</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>文字数(40字)</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>41文字入力</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>40文字で止まる</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>両親情報</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>父 名</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>英字のみ</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>数字入力</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>除去される</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>両親情報</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>母Unknown</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>チェック→非表示</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>「不明/Unknown」にチェック</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>母の姓名入力欄が非表示</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n"/>
+      <c r="H55" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>両親情報</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>母 姓</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>英字のみ+大文字変換</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>「suzuki」入力</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>「SUZUKI」に変換</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n"/>
+      <c r="H56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>両親情報</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>母 名</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>英字のみ+大文字変換</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>「yoko」入力</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>「YOKO」に変換</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="n"/>
+      <c r="H57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>適格性質問</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>質問①</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>デフォルト値</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>質問①を確認</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>はい/いいえ どちらも未選択</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>適格性質問</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>質問①</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>はい選択</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>「はい」クリック</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>「はい」が選択状態になる</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n"/>
+      <c r="H59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>適格性質問</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>質問①</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>いいえ選択</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>「いいえ」クリック</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>「いいえ」が選択状態になる</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n"/>
+      <c r="H60" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>適格性質問</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>質問②〜⑧</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>全問回答</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>各質問で「いいえ」を選択</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>全て正常に選択可能</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="n"/>
+      <c r="H61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>適格性質問</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>質問⑨</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>いいえ選択</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>「いいえ」クリック</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>正常に選択</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="n"/>
+      <c r="H62" s="4" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>適格性質問</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>全問未回答</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>次画面進行</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>全問未選択のまま次画面ボタン</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>進めない/エラー表示</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="n"/>
+      <c r="H63" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>適格性質問</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>注意表示</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>警告ボックス</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>質問セクション上部を確認</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>⚠注意：すべて正直に…が表示</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="n"/>
+      <c r="H64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>同意事項</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>免責事項</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>テキスト表示</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>免責事項のテキストボックスを確認</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>スクロール可能なテキストが表示</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="n"/>
+      <c r="H65" s="4" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>同意事項</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>免責事項</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>スクロール</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>テキストボックスをスクロール</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>全文が閲覧可能</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="n"/>
+      <c r="H66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>同意事項</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>免責事項</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>チェックボックス</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>チェックを入れる</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>チェック状態になる</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="n"/>
+      <c r="H67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>同意事項</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>利用規約</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>テキスト表示</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>利用規約のテキストボックスを確認</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>スクロール可能なテキスト表示</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="n"/>
+      <c r="H68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>同意事項</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>利用規約</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>チェックボックス</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>チェックを入れる</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>チェック状態になる</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="n"/>
+      <c r="H69" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>同意事項</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>両方未チェック</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>次画面進行</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>チェックなしで次画面ボタン</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>進めない/エラー表示</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="n"/>
+      <c r="H70" s="4" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>同意事項</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>片方チェック</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>次画面進行</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>免責のみチェックで次画面</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>進めない</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="n"/>
+      <c r="H71" s="4" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>同意事項</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>両方チェック</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>次画面進行</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>両方チェックして次画面ボタン</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>正常に進む</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="n"/>
+      <c r="H72" s="4" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>緊急連絡先</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>姓</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>苗字アラート</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>緊急連絡先「はい」→姓に「SUZKI」入力→blur</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>⚠️アラート「もしかして SUZUKI ではありませんか？」が表示される</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>CSV仕様対応: attachSurnameAlert適用</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>両親情報</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>父 姓</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>苗字アラート</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>両親「はい」→父の姓に「TNAKA」入力→blur</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>⚠️アラート「もしかして TANAKA ではありませんか？」が表示される</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>CSV仕様対応: attachSurnameAlert適用</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>両親情報</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>母 姓</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>苗字アラート</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>母の姓に「SATOU」入力→blur</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>⚠️アラート「もしかして SATO ではありませんか？」が表示される</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>CSV仕様対応: attachSurnameAlert適用</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H75"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6051,7 +12317,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8390,7 +14656,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9641,7 +15907,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10188,7 +16454,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/ESTA_バリデーション確認テストシート.xlsx
+++ b/ESTA_バリデーション確認テストシート.xlsx
@@ -33,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,8 +46,13 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001A3A5C"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +62,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001a3a5c"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEEFF"/>
+        <bgColor rgb="00DDEEFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -78,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -90,6 +125,19 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -455,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:H145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4255,6 +4303,974 @@
       <c r="H118" s="3" t="inlineStr">
         <is>
           <t>CSV仕様対応: attachSurnameAlert適用</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr"/>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>フェーズ2〜5</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>カメラ機能・自動入力拡張（新規テストケース）</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr"/>
+      <c r="E120" s="5" t="inlineStr"/>
+      <c r="F120" s="5" t="inlineStr"/>
+      <c r="G120" s="5" t="inlineStr"/>
+      <c r="H120" s="5" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>P2-001</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>フェーズ2</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>カメラモーダル</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>スマホで「📷 カメラで撮影」タップ</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>カメラモーダルが全画面表示・ガイドが描画される</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="inlineStr"/>
+      <c r="H121" s="6" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>P2-002</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>フェーズ2</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>人型ガイド</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>カメラ起動時</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>頭部正円＋肩ラインのシルエットが表示される</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr"/>
+      <c r="H122" s="6" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>P2-003</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>フェーズ2</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>明るさNG</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>暗い場所でカメラを向ける</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>「明るい場所で撮影してください」が表示される</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G123" s="6" t="inlineStr"/>
+      <c r="H123" s="6" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>P2-004</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>フェーズ2</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>自動シャッターOFF(デフォルト)</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>カメラ起動直後</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>「🔴 自動 OFF」状態・手動シャッターのみ有効</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr"/>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>P2-005</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>フェーズ2</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>自動シャッターON切替</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>「🔴 自動 OFF」ボタンをタップ</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>「🟢 自動 ON」に変わる</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G125" s="6" t="inlineStr"/>
+      <c r="H125" s="6" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>P2-006</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>フェーズ2</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>自動撮影発火</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>自動ONで明るさOK・顔OKを0.5秒維持</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>「自動撮影します！」ポップアップ後に自動撮影</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr"/>
+      <c r="H126" s="6" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>P2-007</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>フェーズ2</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>品質チェック表示</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>撮影後</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>明るさ・解像度・形式の品質チェック結果が表示される</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G127" s="6" t="inlineStr"/>
+      <c r="H127" s="6" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>P2-008</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>フェーズ2</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>再撮影</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>「再撮影する」をタップ</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>カメラガイドに戻る</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr"/>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>P3-001</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>フェーズ3</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>QRボタン表示</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>PC表示で顔写真欄を表示</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>「📱 スマホから送信（QR）」ボタンが表示される</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr"/>
+      <c r="H129" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>P3-002</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>フェーズ3</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>QR生成</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>「📱 スマホから送信」クリック</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>QRコードとカウントダウンバーが表示される</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr"/>
+      <c r="H130" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>P3-003</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>フェーズ3</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>SP専用UI</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>QRのURLをスマホで開く</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>フォームが非表示→「顔写真をPCに送信」専用UIが表示される</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr"/>
+      <c r="H131" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>P3-004</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>フェーズ3</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>5分タイムアウト</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>QR表示後5分放置</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>QRがグレーアウトし「期限切れ」メッセージが出る</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr"/>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>P3-005</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>フェーズ3</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>SP→PC転送</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>SP側で撮影して送信</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>PC側に写真がプレビュー表示される</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr"/>
+      <c r="H133" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="8" t="inlineStr">
+        <is>
+          <t>P4-001</t>
+        </is>
+      </c>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>フェーズ4</t>
+        </is>
+      </c>
+      <c r="C134" s="8" t="inlineStr">
+        <is>
+          <t>品質スコア表示</t>
+        </is>
+      </c>
+      <c r="D134" s="8" t="inlineStr">
+        <is>
+          <t>撮影後の品質チェック画面</t>
+        </is>
+      </c>
+      <c r="E134" s="8" t="inlineStr">
+        <is>
+          <t>0-100のスコアとゲージバーが表示される</t>
+        </is>
+      </c>
+      <c r="F134" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G134" s="8" t="inlineStr"/>
+      <c r="H134" s="8" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
+          <t>P4-002</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="inlineStr">
+        <is>
+          <t>フェーズ4</t>
+        </is>
+      </c>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t>スコア90以上</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="inlineStr">
+        <is>
+          <t>明るく・顔正面・適切サイズで撮影</t>
+        </is>
+      </c>
+      <c r="E135" s="8" t="inlineStr">
+        <is>
+          <t>✅高品質として「この写真を使用する」ボタンが表示</t>
+        </is>
+      </c>
+      <c r="F135" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr"/>
+      <c r="H135" s="8" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="8" t="inlineStr">
+        <is>
+          <t>P4-003</t>
+        </is>
+      </c>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t>フェーズ4</t>
+        </is>
+      </c>
+      <c r="C136" s="8" t="inlineStr">
+        <is>
+          <t>スコア60未満</t>
+        </is>
+      </c>
+      <c r="D136" s="8" t="inlineStr">
+        <is>
+          <t>暗い・顔が小さいなどNG条件で撮影</t>
+        </is>
+      </c>
+      <c r="E136" s="8" t="inlineStr">
+        <is>
+          <t>❌再撮影推奨・「この写真を使用する」ボタンが非表示</t>
+        </is>
+      </c>
+      <c r="F136" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G136" s="8" t="inlineStr"/>
+      <c r="H136" s="8" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t>P4-004</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>フェーズ4</t>
+        </is>
+      </c>
+      <c r="C137" s="8" t="inlineStr">
+        <is>
+          <t>デバッグパネル</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t>?debug=1でアクセス</t>
+        </is>
+      </c>
+      <c r="E137" s="8" t="inlineStr">
+        <is>
+          <t>撮影統計パネルがページ下部に表示される</t>
+        </is>
+      </c>
+      <c r="F137" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr"/>
+      <c r="H137" s="8" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>P5-001</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>フェーズ5</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>OCR自動起動</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>パスポート画像をアップロード</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="inlineStr">
+        <is>
+          <t>処理完了後「🔍 パスポートを読み取り中」が自動表示される</t>
+        </is>
+      </c>
+      <c r="F138" s="9" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G138" s="9" t="inlineStr"/>
+      <c r="H138" s="9" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>P5-002</t>
+        </is>
+      </c>
+      <c r="B139" s="9" t="inlineStr">
+        <is>
+          <t>フェーズ5</t>
+        </is>
+      </c>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t>OCR自動入力</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>日本パスポートをアップロード</t>
+        </is>
+      </c>
+      <c r="E139" s="9" t="inlineStr">
+        <is>
+          <t>姓・名・パスポート番号・生年月日・有効期限・性別が自動入力される</t>
+        </is>
+      </c>
+      <c r="F139" s="9" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G139" s="9" t="inlineStr"/>
+      <c r="H139" s="9" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>P5-003</t>
+        </is>
+      </c>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>フェーズ5</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t>OCR読取失敗</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>ぼやけた画像をアップロード</t>
+        </is>
+      </c>
+      <c r="E140" s="9" t="inlineStr">
+        <is>
+          <t>「❌ MRZを読み取れませんでした」と「🔄 再読み取り」ボタンが表示</t>
+        </is>
+      </c>
+      <c r="F140" s="9" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G140" s="9" t="inlineStr"/>
+      <c r="H140" s="9" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="9" t="inlineStr">
+        <is>
+          <t>P5-004</t>
+        </is>
+      </c>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>フェーズ5</t>
+        </is>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>入力履歴保存</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>Step1入力後にStep2へ進む</t>
+        </is>
+      </c>
+      <c r="E141" s="9" t="inlineStr">
+        <is>
+          <t>localStorageにフォームデータが保存される</t>
+        </is>
+      </c>
+      <c r="F141" s="9" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G141" s="9" t="inlineStr"/>
+      <c r="H141" s="9" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>P5-005</t>
+        </is>
+      </c>
+      <c r="B142" s="9" t="inlineStr">
+        <is>
+          <t>フェーズ5</t>
+        </is>
+      </c>
+      <c r="C142" s="9" t="inlineStr">
+        <is>
+          <t>入力履歴復元</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="inlineStr">
+        <is>
+          <t>保存後にページをリロード</t>
+        </is>
+      </c>
+      <c r="E142" s="9" t="inlineStr">
+        <is>
+          <t>「📋 前回の入力内容があります」バーが表示される</t>
+        </is>
+      </c>
+      <c r="F142" s="9" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G142" s="9" t="inlineStr"/>
+      <c r="H142" s="9" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="9" t="inlineStr">
+        <is>
+          <t>P5-006</t>
+        </is>
+      </c>
+      <c r="B143" s="9" t="inlineStr">
+        <is>
+          <t>フェーズ5</t>
+        </is>
+      </c>
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>復元実行</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="inlineStr">
+        <is>
+          <t>「復元する」ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="E143" s="9" t="inlineStr">
+        <is>
+          <t>前回入力した値が各フィールドに復元される</t>
+        </is>
+      </c>
+      <c r="F143" s="9" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G143" s="9" t="inlineStr"/>
+      <c r="H143" s="9" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>P5-007</t>
+        </is>
+      </c>
+      <c r="B144" s="9" t="inlineStr">
+        <is>
+          <t>フェーズ5</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>メールサジェスト</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="inlineStr">
+        <is>
+          <t>emailフィールドで「test@」を入力</t>
+        </is>
+      </c>
+      <c r="E144" s="9" t="inlineStr">
+        <is>
+          <t>gmail.com等のドメイン候補が最大4件表示される</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G144" s="9" t="inlineStr"/>
+      <c r="H144" s="9" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>P5-008</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>フェーズ5</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>サジェスト選択</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>サジェストのドメインをクリック</t>
+        </is>
+      </c>
+      <c r="E145" s="9" t="inlineStr">
+        <is>
+          <t>メールアドレスが補完される</t>
+        </is>
+      </c>
+      <c r="F145" s="9" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G145" s="9" t="inlineStr"/>
+      <c r="H145" s="9" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
         </is>
       </c>
     </row>
